--- a/Images/1/100StatisticalSeries.xlsx
+++ b/Images/1/100StatisticalSeries.xlsx
@@ -457,96 +457,96 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="G2">
-        <v>8</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
       <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
         <v>6</v>
       </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
       <c r="K2">
+        <v>14</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2">
         <v>5</v>
       </c>
-      <c r="L2">
-        <v>8</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
-      </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
       <c r="O2">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="B3">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C3">
-        <v>0.02</v>
+        <v>0.04000000000000001</v>
       </c>
       <c r="D3">
-        <v>0.04000000000000001</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="E3">
-        <v>0.1</v>
+        <v>0.06000000000000003</v>
       </c>
       <c r="F3">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G3">
+        <v>0.06999999999999995</v>
+      </c>
+      <c r="H3">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="I3">
         <v>0.04999999999999999</v>
       </c>
-      <c r="G3">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="H3">
-        <v>0.13</v>
-      </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.05999999999999994</v>
       </c>
-      <c r="J3">
-        <v>0.09000000000000008</v>
-      </c>
       <c r="K3">
+        <v>0.14</v>
+      </c>
+      <c r="L3">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="M3">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="N3">
         <v>0.04999999999999993</v>
       </c>
-      <c r="L3">
-        <v>0.08000000000000007</v>
-      </c>
-      <c r="M3">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="N3">
-        <v>0.03999999999999992</v>
-      </c>
       <c r="O3">
-        <v>0.05000000000000004</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>

--- a/Images/1/100StatisticalSeries.xlsx
+++ b/Images/1/100StatisticalSeries.xlsx
@@ -457,96 +457,96 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
         <v>7</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
         <v>7</v>
       </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>14</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>6</v>
-      </c>
       <c r="N2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O2">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="B3">
+        <v>0.04</v>
+      </c>
+      <c r="C3">
+        <v>0.14</v>
+      </c>
+      <c r="D3">
+        <v>0.05000000000000002</v>
+      </c>
+      <c r="E3">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="F3">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="G3">
+        <v>0.02999999999999997</v>
+      </c>
+      <c r="H3">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C3">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="D3">
-        <v>0.03999999999999998</v>
-      </c>
-      <c r="E3">
-        <v>0.06000000000000003</v>
-      </c>
-      <c r="F3">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G3">
+      <c r="I3">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="J3">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="K3">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="L3">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="M3">
         <v>0.06999999999999995</v>
       </c>
-      <c r="H3">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="I3">
-        <v>0.04999999999999999</v>
-      </c>
-      <c r="J3">
-        <v>0.05999999999999994</v>
-      </c>
-      <c r="K3">
-        <v>0.14</v>
-      </c>
-      <c r="L3">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="M3">
-        <v>0.06000000000000005</v>
-      </c>
       <c r="N3">
-        <v>0.04999999999999993</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="O3">
-        <v>0.14</v>
+        <v>0.07999999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/Images/1/100StatisticalSeries.xlsx
+++ b/Images/1/100StatisticalSeries.xlsx
@@ -16,70 +16,73 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t>[ 2.000000,
- 2.266667 )</t>
-  </si>
-  <si>
-    <t>[ 2.266667,
- 2.533333 )</t>
-  </si>
-  <si>
-    <t>[ 2.533333,
- 2.800000 )</t>
-  </si>
-  <si>
-    <t>[ 2.800000,
- 3.066667 )</t>
-  </si>
-  <si>
-    <t>[ 3.066667,
- 3.333333 )</t>
-  </si>
-  <si>
-    <t>[ 3.333333,
- 3.600000 )</t>
-  </si>
-  <si>
-    <t>[ 3.600000,
- 3.866667 )</t>
-  </si>
-  <si>
-    <t>[ 3.866667,
- 4.133333 )</t>
-  </si>
-  <si>
-    <t>[ 4.133333,
- 4.400000 )</t>
-  </si>
-  <si>
-    <t>[ 4.400000,
- 4.666667 )</t>
-  </si>
-  <si>
-    <t>[ 4.666667,
- 4.933333 )</t>
-  </si>
-  <si>
-    <t>[ 4.933333,
- 5.200000 )</t>
-  </si>
-  <si>
-    <t>[ 5.200000,
- 5.466667 )</t>
-  </si>
-  <si>
-    <t>[ 5.466667,
- 5.733333 )</t>
-  </si>
-  <si>
-    <t>[ 5.733333,
- 6.000000 ]</t>
+    <t>[ 2.0,
+ 2.267 )</t>
+  </si>
+  <si>
+    <t>[ 2.267,
+ 2.533 )</t>
+  </si>
+  <si>
+    <t>[ 2.533,
+ 2.8 )</t>
+  </si>
+  <si>
+    <t>[ 2.8,
+ 3.067 )</t>
+  </si>
+  <si>
+    <t>[ 3.067,
+ 3.333 )</t>
+  </si>
+  <si>
+    <t>[ 3.333,
+ 3.6 )</t>
+  </si>
+  <si>
+    <t>[ 3.6,
+ 3.867 )</t>
+  </si>
+  <si>
+    <t>[ 3.867,
+ 4.133 )</t>
+  </si>
+  <si>
+    <t>[ 4.133,
+ 4.4 )</t>
+  </si>
+  <si>
+    <t>[ 4.4,
+ 4.667 )</t>
+  </si>
+  <si>
+    <t>[ 4.667,
+ 4.933 )</t>
+  </si>
+  <si>
+    <t>[ 4.933,
+ 5.2 )</t>
+  </si>
+  <si>
+    <t>[ 5.2,
+ 5.467 )</t>
+  </si>
+  <si>
+    <t>[ 5.467,
+ 5.733 )</t>
+  </si>
+  <si>
+    <t>[ 5.733,
+ 6.0 ]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -97,7 +100,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -105,12 +108,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,147 +424,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.03999999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.05999999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.06000000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.08999999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.06000000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.06999999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.05000000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>14</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
+      <c r="B15">
         <v>8</v>
       </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>10</v>
-      </c>
-      <c r="M2">
-        <v>7</v>
-      </c>
-      <c r="N2">
-        <v>7</v>
-      </c>
-      <c r="O2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3">
-        <v>0.04</v>
-      </c>
-      <c r="B3">
-        <v>0.04</v>
-      </c>
-      <c r="C3">
-        <v>0.14</v>
-      </c>
-      <c r="D3">
-        <v>0.05000000000000002</v>
-      </c>
-      <c r="E3">
-        <v>0.08999999999999997</v>
-      </c>
-      <c r="F3">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="G3">
-        <v>0.02999999999999997</v>
-      </c>
-      <c r="H3">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I3">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="J3">
-        <v>0.07000000000000006</v>
-      </c>
-      <c r="K3">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="L3">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="M3">
-        <v>0.06999999999999995</v>
-      </c>
-      <c r="N3">
-        <v>0.07000000000000006</v>
-      </c>
-      <c r="O3">
+      <c r="C15" s="1">
         <v>0.07999999999999996</v>
       </c>
     </row>
